--- a/imports/rooting_interests.xlsx.xlsx
+++ b/imports/rooting_interests.xlsx.xlsx
@@ -13,14 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="99">
+  <si>
+    <t>What the importer accepts</t>
+  </si>
   <si>
     <t>Stat</t>
   </si>
   <si>
-    <t>What the importer accepts</t>
-  </si>
-  <si>
     <t>Direction</t>
   </si>
   <si>
@@ -30,42 +30,81 @@
     <t>pass yds</t>
   </si>
   <si>
+    <t>Goal syntax</t>
+  </si>
+  <si>
+    <t>over N</t>
+  </si>
+  <si>
     <t>over</t>
   </si>
   <si>
+    <t>strictly greater than N</t>
+  </si>
+  <si>
     <t>ARI</t>
   </si>
   <si>
+    <t>under N</t>
+  </si>
+  <si>
+    <t>N or fewer; only settles when the game ends</t>
+  </si>
+  <si>
     <t>pass TD</t>
   </si>
   <si>
+    <t>at least N</t>
+  </si>
+  <si>
     <t>under</t>
   </si>
   <si>
+    <t>shorthand for over N-1</t>
+  </si>
+  <si>
     <t>ATL</t>
   </si>
   <si>
+    <t>any TD</t>
+  </si>
+  <si>
     <t>completions</t>
   </si>
   <si>
+    <t>at least one touchdown; leave Direction and Target blank</t>
+  </si>
+  <si>
     <t>at least</t>
   </si>
   <si>
+    <t>win</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
-    <t>Goal syntax</t>
+    <t>team goal; leave Player, Direction and Target blank</t>
+  </si>
+  <si>
+    <t>points over N</t>
   </si>
   <si>
     <t>attempts</t>
   </si>
   <si>
+    <t>team scores more than N</t>
+  </si>
+  <si>
     <t>(none)</t>
   </si>
   <si>
     <t>BUF</t>
   </si>
   <si>
+    <t>Player stats</t>
+  </si>
+  <si>
     <t>interceptions</t>
   </si>
   <si>
@@ -81,147 +120,111 @@
     <t>rush TD</t>
   </si>
   <si>
-    <t>over N</t>
-  </si>
-  <si>
     <t>CIN</t>
   </si>
   <si>
-    <t>strictly greater than N</t>
-  </si>
-  <si>
     <t>carries</t>
   </si>
   <si>
     <t>CLE</t>
   </si>
   <si>
-    <t>under N</t>
-  </si>
-  <si>
     <t>rec</t>
   </si>
   <si>
-    <t>N or fewer; only settles when the game ends</t>
-  </si>
-  <si>
     <t>DAL</t>
   </si>
   <si>
-    <t>at least N</t>
-  </si>
-  <si>
     <t>rec yds</t>
   </si>
   <si>
-    <t>shorthand for over N-1</t>
-  </si>
-  <si>
     <t>DEN</t>
   </si>
   <si>
-    <t>any TD</t>
-  </si>
-  <si>
     <t>rec TD</t>
   </si>
   <si>
-    <t>at least one touchdown; leave Direction and Target blank</t>
-  </si>
-  <si>
     <t>DET</t>
   </si>
   <si>
-    <t>win</t>
-  </si>
-  <si>
     <t>targets</t>
   </si>
   <si>
-    <t>team goal; leave Player, Direction and Target blank</t>
-  </si>
-  <si>
     <t>GB</t>
   </si>
   <si>
-    <t>points over N</t>
-  </si>
-  <si>
-    <t>team scores more than N</t>
+    <t>tackles</t>
   </si>
   <si>
     <t>HOU</t>
   </si>
   <si>
-    <t>tackles</t>
+    <t>solo tackles</t>
   </si>
   <si>
     <t>IND</t>
   </si>
   <si>
-    <t>Player stats</t>
-  </si>
-  <si>
-    <t>solo tackles</t>
+    <t>sacks</t>
+  </si>
+  <si>
+    <t>tackles for loss</t>
+  </si>
+  <si>
+    <t>passes defended</t>
+  </si>
+  <si>
+    <t>interceptions caught</t>
   </si>
   <si>
     <t>JAX</t>
   </si>
   <si>
-    <t>sacks</t>
+    <t>field goals</t>
+  </si>
+  <si>
+    <t>kicking points</t>
   </si>
   <si>
     <t>KC</t>
   </si>
   <si>
-    <t>tackles for loss</t>
+    <t>fumbles</t>
+  </si>
+  <si>
+    <t>fumbles lost</t>
   </si>
   <si>
     <t>LAC</t>
   </si>
   <si>
-    <t>passes defended</t>
+    <t>Team stats</t>
   </si>
   <si>
     <t>LAR</t>
   </si>
   <si>
-    <t>interceptions caught</t>
+    <t>points</t>
   </si>
   <si>
     <t>LV</t>
   </si>
   <si>
-    <t>field goals</t>
-  </si>
-  <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>kicking points</t>
-  </si>
-  <si>
     <t>MIN</t>
   </si>
   <si>
-    <t>fumbles</t>
-  </si>
-  <si>
     <t>NE</t>
   </si>
   <si>
-    <t>fumbles lost</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
     <t>NYG</t>
   </si>
   <si>
-    <t>points</t>
-  </si>
-  <si>
     <t>NYJ</t>
   </si>
   <si>
@@ -231,30 +234,27 @@
     <t>PIT</t>
   </si>
   <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>TEN</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
     <t>Rooting interests</t>
   </si>
   <si>
-    <t>SEA</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>TEN</t>
-  </si>
-  <si>
-    <t>WSH</t>
-  </si>
-  <si>
     <t>Week</t>
   </si>
   <si>
-    <t>Team stats</t>
-  </si>
-  <si>
     <t>Fill the shaded cells. Leave Player blank for a team goal. Leave Direction and Target blank when the Stat is 'win' or 'any TD'.</t>
   </si>
   <si>
@@ -264,10 +264,52 @@
     <t>BOZO?</t>
   </si>
   <si>
-    <t>Drake Maye 230+ Pass Yds</t>
-  </si>
-  <si>
-    <t>Demario Douglas 3+ Rec Yds</t>
+    <t>Marvin Harrison 3+ Receptions</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Trey McBride 6+ Receptions</t>
+  </si>
+  <si>
+    <t>Bijan Robinson Anytime TD</t>
+  </si>
+  <si>
+    <t>Christian McCaffrey Anytime TD</t>
+  </si>
+  <si>
+    <t>Derrick Henry 70+ Rushing Yds</t>
+  </si>
+  <si>
+    <t>Jaxon Smith-Njigba 7+ Receptions</t>
+  </si>
+  <si>
+    <t>Cincinnati Bengals Moneyline</t>
+  </si>
+  <si>
+    <t>Carolina Panthers Moneyline</t>
+  </si>
+  <si>
+    <t>San Francisco 49ers -2.5 Spread</t>
+  </si>
+  <si>
+    <t>Los Angeles Rams -3.5 Spread</t>
+  </si>
+  <si>
+    <t>Josh Jacobs Anytime TD</t>
+  </si>
+  <si>
+    <t>Kenneth Walker III Anytime TD</t>
+  </si>
+  <si>
+    <t>Brock Bowers 60+ Receiving Yds</t>
+  </si>
+  <si>
+    <t>C.J. Stroud 230+ Passing Yds</t>
+  </si>
+  <si>
+    <t>Jahmyr Gibbs 130+ Rushing + Receiving Yds</t>
   </si>
 </sst>
 </file>
@@ -283,20 +325,15 @@
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13.0"/>
       <color rgb="FF1F2937"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -308,6 +345,11 @@
       <sz val="10.0"/>
       <color rgb="FF1F2937"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -423,13 +465,13 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
@@ -452,10 +494,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
@@ -463,13 +502,21 @@
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="3" fillId="2" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -477,6 +524,7 @@
     <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -756,12 +804,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" s="8">
         <v>7.0</v>
@@ -788,319 +836,396 @@
         <v>83</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="15"/>
+        <v>47</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="H8" s="17"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="16"/>
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="16"/>
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="16"/>
-      <c r="H11" s="17"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="16"/>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="16"/>
-      <c r="F13" s="18"/>
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="16"/>
-      <c r="F14" s="18"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="16"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="16"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="16"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="16"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13"/>
       <c r="C19" s="19"/>
     </row>
     <row r="20">
-      <c r="A20" s="13"/>
-      <c r="B20" s="20"/>
+      <c r="A20" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="C20" s="19"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="21"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="24"/>
+      <c r="A21" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="24"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="21"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="24"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="24"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="24"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="25"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="24"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="25"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="21"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="24"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="21"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="24"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="21"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="24"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="21"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="24"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="21"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="24"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="25"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="21"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="24"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="21"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="24"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="21"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="24"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="21"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="24"/>
+      <c r="A36" s="26"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="25"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="21"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="24"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="25"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="21"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="24"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="21"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="24"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="21"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="24"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="25"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="21"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="24"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="25"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="21"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="24"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="25"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="21"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="24"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="25"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="21"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="24"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="25"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="21"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="24"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="25"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="21"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="24"/>
+      <c r="A46" s="26"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" ht="15.75" customHeight="1"/>
     <row r="48" ht="15.75" customHeight="1"/>
@@ -2079,260 +2204,260 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
+      <c r="A4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
+      <c r="A5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="C14" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
+      <c r="C25" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>69</v>
+      <c r="C26" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="C27" s="2" t="s">
-        <v>70</v>
+      <c r="C27" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="C28" s="2" t="s">
-        <v>71</v>
+      <c r="C28" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="5" t="s">
         <v>77</v>
       </c>
     </row>
@@ -3324,237 +3449,237 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="3"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="4"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="4"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="4"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="4"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="4" t="s">
+      <c r="B38" s="3"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="4"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="4"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" s="4"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="4"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="4"/>
+      <c r="B39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
